--- a/momentum/Alpha_LowVol/n500_alphavol.xlsx
+++ b/momentum/Alpha_LowVol/n500_alphavol.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP20" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CALCS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TOP20" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CALCS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -578,7 +578,7 @@
         <v>2.270826103436008</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.1879713520791655</v>
+        <v>0.1879713520791654</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>5.223261401281236</v>
@@ -603,7 +603,7 @@
         <v>1.901710058053072</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>0.2343654877217925</v>
+        <v>0.2343654877217924</v>
       </c>
       <c r="G4" s="10" t="n">
         <v>4.916261360999032</v>
@@ -622,13 +622,13 @@
         <v>1.207886165258611</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>-0.04356395299334061</v>
+        <v>-0.04356395299333968</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>2.459336283510563</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.06523576182496738</v>
+        <v>0.06523576182496749</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>5.380048497373074</v>
@@ -647,13 +647,13 @@
         <v>1.15760727171273</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>-0.1920731875382238</v>
+        <v>-0.1920731875382237</v>
       </c>
       <c r="E6" s="10" t="n">
         <v>2.507287730963685</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.02268895836041095</v>
+        <v>0.02268895836041082</v>
       </c>
       <c r="G6" s="10" t="n">
         <v>5.419930524946343</v>
@@ -672,13 +672,13 @@
         <v>1.131098660425734</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>-0.610065949800458</v>
+        <v>-0.6100659498004583</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>2.872263270651926</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.09706289383975303</v>
+        <v>-0.09706289383975322</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>5.723486836810451</v>
@@ -703,7 +703,7 @@
         <v>0.6219634507686145</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0.5161413063331004</v>
+        <v>0.5161413063331001</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>3.851874524117559</v>
@@ -719,16 +719,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1.074980023331861</v>
+        <v>1.074980023331862</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>-0.1359258430973462</v>
+        <v>-0.1359258430973453</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>2.285885889761068</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.03877475959899178</v>
+        <v>0.0387747595989919</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>5.235786879559045</v>
@@ -747,13 +747,13 @@
         <v>1.037727272393083</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.08785414499910993</v>
+        <v>0.08785414499911037</v>
       </c>
       <c r="E10" s="10" t="n">
         <v>1.987600399787056</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>0.102886080366477</v>
+        <v>0.1028860803664769</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>4.987697806805201</v>
@@ -772,13 +772,13 @@
         <v>1.017994754840768</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>-0.2408202671777974</v>
+        <v>-0.2408202671777971</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>2.276809776859333</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.008723278561090512</v>
+        <v>0.00872327856109042</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>5.22823812338523</v>
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0.9410939437319552</v>
+        <v>0.9410939437319554</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.1486605011324833</v>
+        <v>0.1486605011324838</v>
       </c>
       <c r="E12" s="10" t="n">
         <v>1.733527386331427</v>
@@ -819,16 +819,16 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.9308807787250277</v>
+        <v>0.9308807787250282</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1.502359971381</v>
+        <v>1.502359971381001</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>0.3594015860690558</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.508131596438082</v>
+        <v>0.5081315964380821</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>3.633497393002301</v>
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>0.9295884667472715</v>
+        <v>0.9295884667472712</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>-0.1606814052878323</v>
+        <v>-0.1606814052878327</v>
       </c>
       <c r="E14" s="10" t="n">
         <v>2.019858338782375</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>0.03168247309976475</v>
+        <v>0.03168247309976448</v>
       </c>
       <c r="G14" s="10" t="n">
         <v>5.0145272787148</v>
@@ -872,13 +872,13 @@
         <v>0.8836082953455413</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.6425694369647593</v>
+        <v>0.6425694369647594</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>1.124647153726323</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.2618079317811349</v>
+        <v>0.2618079317811348</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>4.269965037893848</v>
@@ -894,16 +894,16 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>0.8827666883463003</v>
+        <v>0.8827666883463005</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.4443933121626876</v>
+        <v>0.4443933121626877</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>1.321140064529913</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>0.205031929540191</v>
+        <v>0.2050319295401909</v>
       </c>
       <c r="G16" s="10" t="n">
         <v>4.433391505765998</v>
@@ -919,16 +919,16 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.877261092579662</v>
+        <v>0.8772610925796609</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1.725185968680469</v>
+        <v>1.725185968680466</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>0.02933621647885534</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.5719696058584931</v>
+        <v>0.5719696058584923</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>3.358976458387205</v>
@@ -944,16 +944,16 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>0.838910693515946</v>
+        <v>0.8389106935159458</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.143494800934097</v>
+        <v>0.1434948009340965</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>1.534326586097795</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>0.1188267190746337</v>
+        <v>0.1188267190746334</v>
       </c>
       <c r="G18" s="10" t="n">
         <v>4.61070233125738</v>
@@ -972,13 +972,13 @@
         <v>0.8300265731636719</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.258899424960407</v>
+        <v>0.2588994249604071</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>1.401153721366937</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.1518892950982445</v>
+        <v>0.1518892950982443</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>4.499940213629968</v>
@@ -1003,7 +1003,7 @@
         <v>0.4850001151536185</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>0.3703414468186803</v>
+        <v>0.3703414468186801</v>
       </c>
       <c r="G20" s="10" t="n">
         <v>3.737959807927515</v>
@@ -1022,13 +1022,13 @@
         <v>0.7312452273445067</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>-0.4584417415257167</v>
+        <v>-0.4584417415257168</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>1.92093219621473</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>-0.05362367331111514</v>
+        <v>-0.05362367331111532</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>4.932248737499604</v>
@@ -1044,16 +1044,16 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>0.7163107559626355</v>
+        <v>0.7163107559626349</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.02251560209182702</v>
+        <v>0.02251560209182591</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>1.410105909833444</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>0.08416706836526376</v>
+        <v>0.08416706836526329</v>
       </c>
       <c r="G22" s="10" t="n">
         <v>4.507385899760952</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C3" s="6" t="n">
-        <v>0.1879713520791655</v>
+        <v>0.1879713520791654</v>
       </c>
       <c r="D3" s="6" t="n">
         <v>0.3848435200909697</v>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>0.2343654877217925</v>
+        <v>0.2343654877217924</v>
       </c>
       <c r="D4" s="10" t="n">
         <v>0.5467818329749843</v>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.06523576182496738</v>
+        <v>0.06523576182496749</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>-0.04356395299334061</v>
+        <v>-0.04356395299333968</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>5.380048497373074</v>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.02268895836041095</v>
+        <v>0.02268895836041082</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>-0.1920731875382238</v>
+        <v>-0.1920731875382237</v>
       </c>
       <c r="E6" s="10" t="n">
         <v>5.419930524946343</v>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>-0.09706289383975303</v>
+        <v>-0.09706289383975322</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>-0.610065949800458</v>
+        <v>-0.6100659498004583</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>5.723486836810451</v>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>0.5161413063331004</v>
+        <v>0.5161413063331001</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>1.530317791677104</v>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.03877475959899178</v>
+        <v>0.0387747595989919</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>-0.1359258430973462</v>
+        <v>-0.1359258430973453</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>5.235786879559045</v>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>0.102886080366477</v>
+        <v>0.1028860803664769</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.08785414499910993</v>
+        <v>0.08785414499911037</v>
       </c>
       <c r="E10" s="10" t="n">
         <v>4.987697806805201</v>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0.008723278561090512</v>
+        <v>0.00872327856109042</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>-0.2408202671777974</v>
+        <v>-0.2408202671777971</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>5.22823812338523</v>
@@ -1334,7 +1334,7 @@
         <v>0.1203066541895854</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.1486605011324833</v>
+        <v>0.1486605011324838</v>
       </c>
       <c r="E12" s="10" t="n">
         <v>4.776380996438482</v>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>0.508131596438082</v>
+        <v>0.5081315964380821</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1.502359971381</v>
+        <v>1.502359971381001</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>3.633497393002301</v>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>0.03168247309976475</v>
+        <v>0.03168247309976448</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>-0.1606814052878323</v>
+        <v>-0.1606814052878327</v>
       </c>
       <c r="E14" s="10" t="n">
         <v>5.0145272787148</v>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0.2618079317811349</v>
+        <v>0.2618079317811348</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.6425694369647593</v>
+        <v>0.6425694369647594</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>4.269965037893848</v>
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>0.205031929540191</v>
+        <v>0.2050319295401909</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.4443933121626876</v>
+        <v>0.4443933121626877</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>4.433391505765998</v>
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.5719696058584931</v>
+        <v>0.5719696058584923</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1.725185968680469</v>
+        <v>1.725185968680466</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>3.358976458387205</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>0.1188267190746337</v>
+        <v>0.1188267190746334</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.143494800934097</v>
+        <v>0.1434948009340965</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>4.61070233125738</v>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.1518892950982445</v>
+        <v>0.1518892950982443</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.258899424960407</v>
+        <v>0.2588994249604071</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>4.499940213629968</v>
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>0.3703414468186803</v>
+        <v>0.3703414468186801</v>
       </c>
       <c r="D20" s="10" t="n">
         <v>1.021404694333006</v>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>-0.05362367331111514</v>
+        <v>-0.05362367331111532</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>-0.4584417415257167</v>
+        <v>-0.4584417415257168</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>4.932248737499604</v>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>0.08416706836526376</v>
+        <v>0.08416706836526329</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.02251560209182702</v>
+        <v>0.02251560209182591</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>4.507385899760952</v>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>0.353135836131488</v>
+        <v>0.3531358361314875</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0.9613486650907436</v>
+        <v>0.961348665090742</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>3.682385941117751</v>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>0.4801356907806155</v>
+        <v>0.4801356907806154</v>
       </c>
       <c r="D24" s="10" t="n">
         <v>1.404640514664477</v>
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>0.381857036419839</v>
+        <v>0.3818570364198391</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1.061599756188258</v>
+        <v>1.061599756188259</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>3.558509783903506</v>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>-0.03140442056337089</v>
+        <v>-0.03140442056337109</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>-0.3808856397970485</v>
+        <v>-0.3808856397970487</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>4.71576683404415</v>
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>0.04412690788514632</v>
+        <v>0.04412690788514609</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>-0.1172442176772447</v>
+        <v>-0.117244217677245</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>4.49600168676515</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>0.3359141226915172</v>
+        <v>0.335914122691517</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.9012364293348427</v>
+        <v>0.9012364293348424</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>3.599659772469325</v>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>0.004026476377834</v>
+        <v>0.004026476377833817</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>-0.2572144129242628</v>
+        <v>-0.2572144129242629</v>
       </c>
       <c r="E29" s="6" t="n">
         <v>4.54303546271201</v>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>0.5401938268220196</v>
+        <v>0.5401938268220194</v>
       </c>
       <c r="D30" s="10" t="n">
         <v>1.614272897955774</v>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>-0.1424758122058082</v>
+        <v>-0.142475812205808</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>-0.768579332612175</v>
+        <v>-0.7685793326121738</v>
       </c>
       <c r="E31" s="6" t="n">
         <v>4.940455861494351</v>
@@ -1771,10 +1771,10 @@
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>0.1154185310109974</v>
+        <v>0.1154185310109971</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.1315985511738234</v>
+        <v>0.1315985511738229</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>4.189833926041008</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>-0.05918264420198471</v>
+        <v>-0.05918264420198486</v>
       </c>
       <c r="D33" s="6" t="n">
         <v>-0.4778452793860417</v>
@@ -1815,10 +1815,10 @@
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>0.15266274521273</v>
+        <v>0.1526627452127297</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.2615991456234782</v>
+        <v>0.261599145623478</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>4.064897476824568</v>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.2390406002698223</v>
+        <v>0.2390406002698221</v>
       </c>
       <c r="D35" s="6" t="n">
         <v>0.5631002712449112</v>
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>0.7543015997692771</v>
+        <v>0.7543015997692767</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>2.361614152322752</v>
+        <v>2.361614152322751</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>2.234030350467135</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.3763988482729141</v>
+        <v>0.3763988482729138</v>
       </c>
       <c r="D37" s="6" t="n">
         <v>1.042547999588563</v>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>-0.06195499112019027</v>
+        <v>-0.06195499112019041</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>-0.4875221313511619</v>
+        <v>-0.4875221313511618</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>4.59161978821526</v>
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>0.7573379755341353</v>
+        <v>0.7573379755341351</v>
       </c>
       <c r="D39" s="6" t="n">
         <v>2.372212594600686</v>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>0.1713018048765949</v>
+        <v>0.1713018048765947</v>
       </c>
       <c r="D40" s="10" t="n">
         <v>0.3266586156168685</v>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="C41" s="6" t="n">
-        <v>0.1645265081602505</v>
+        <v>0.1645265081602501</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>0.3030095034104257</v>
+        <v>0.303009503410425</v>
       </c>
       <c r="E41" s="6" t="n">
         <v>3.89063009306882</v>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>0.5421199037059106</v>
+        <v>0.5421199037059103</v>
       </c>
       <c r="D42" s="10" t="n">
         <v>1.620995851983085</v>
@@ -2016,7 +2016,7 @@
         <v>0.1162715253093537</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>0.1345759200947475</v>
+        <v>0.134575920094748</v>
       </c>
       <c r="E43" s="6" t="n">
         <v>3.994139081847006</v>
@@ -2035,10 +2035,10 @@
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>0.4444598608898945</v>
+        <v>0.4444598608898949</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1.280114351535957</v>
+        <v>1.280114351535959</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>3.039200075514576</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>0.2011958071312531</v>
+        <v>0.2011958071312529</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>0.4310033614218185</v>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>-0.1283260325161149</v>
+        <v>-0.1283260325161151</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>-0.7191896539622705</v>
+        <v>-0.7191896539622707</v>
       </c>
       <c r="E46" s="10" t="n">
         <v>4.679589491463434</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>0.6154709745410701</v>
+        <v>0.6154709745410702</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>1.877027104527162</v>
+        <v>1.877027104527163</v>
       </c>
       <c r="E47" s="6" t="n">
         <v>2.507907836386273</v>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>-0.1631641315974461</v>
+        <v>-0.1631641315974462</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>-0.8407917252407231</v>
+        <v>-0.8407917252407229</v>
       </c>
       <c r="E48" s="10" t="n">
         <v>4.761391964706035</v>
@@ -2148,7 +2148,7 @@
         <v>0.2917637593644565</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>0.7471299835229416</v>
+        <v>0.7471299835229421</v>
       </c>
       <c r="E49" s="6" t="n">
         <v>3.432386825042431</v>
@@ -2170,7 +2170,7 @@
         <v>0.1834506315605235</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>0.3690639858099948</v>
+        <v>0.3690639858099951</v>
       </c>
       <c r="E50" s="10" t="n">
         <v>3.743088720352606</v>
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>0.1697537334111449</v>
+        <v>0.1697537334111446</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>0.3212550861003381</v>
+        <v>0.3212550861003375</v>
       </c>
       <c r="E51" s="6" t="n">
         <v>3.769963050959042</v>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>0.2154737730199942</v>
+        <v>0.215473773019994</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>0.4808404728457427</v>
+        <v>0.4808404728457423</v>
       </c>
       <c r="E52" s="10" t="n">
         <v>3.629352655921471</v>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="C53" s="6" t="n">
-        <v>0.1579590708567294</v>
+        <v>0.1579590708567291</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>0.2800859226135766</v>
+        <v>0.2800859226135761</v>
       </c>
       <c r="E53" s="6" t="n">
         <v>3.788073071995045</v>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>0.6767600756565563</v>
+        <v>0.6767600756565559</v>
       </c>
       <c r="D54" s="10" t="n">
-        <v>2.090956160330078</v>
+        <v>2.090956160330077</v>
       </c>
       <c r="E54" s="10" t="n">
         <v>2.27729635083046</v>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="C55" s="6" t="n">
-        <v>-0.05031265782362197</v>
+        <v>-0.05031265782362213</v>
       </c>
       <c r="D55" s="6" t="n">
         <v>-0.4468846717678562</v>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>0.4148276669076511</v>
+        <v>0.4148276669076509</v>
       </c>
       <c r="D56" s="10" t="n">
         <v>1.176683445149431</v>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="C57" s="6" t="n">
-        <v>0.3354579683177241</v>
+        <v>0.3354579683177238</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>0.8996442265987957</v>
+        <v>0.8996442265987952</v>
       </c>
       <c r="E57" s="6" t="n">
         <v>3.236742499866958</v>
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>0.7825799318926381</v>
+        <v>0.7825799318926377</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>2.460319416076462</v>
+        <v>2.460319416076461</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>1.925082882185517</v>
@@ -2368,7 +2368,7 @@
         <v>0.3356975881454842</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>0.9004806174508625</v>
+        <v>0.9004806174508629</v>
       </c>
       <c r="E59" s="6" t="n">
         <v>3.170849393228826</v>
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>0.158707410302404</v>
+        <v>0.1587074103024035</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>0.2826979947131751</v>
+        <v>0.282697994713174</v>
       </c>
       <c r="E60" s="10" t="n">
         <v>3.668782222911385</v>
@@ -2409,10 +2409,10 @@
         </is>
       </c>
       <c r="C61" s="6" t="n">
-        <v>0.1228224928532771</v>
+        <v>0.1228224928532768</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>0.1574420133439595</v>
+        <v>0.1574420133439591</v>
       </c>
       <c r="E61" s="6" t="n">
         <v>3.754813738544243</v>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>0.3722290175008877</v>
+        <v>0.3722290175008875</v>
       </c>
       <c r="D62" s="10" t="n">
         <v>1.02799324280992</v>
@@ -2453,10 +2453,10 @@
         </is>
       </c>
       <c r="C63" s="6" t="n">
-        <v>0.02807544676264188</v>
+        <v>0.02807544676264164</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>-0.1732716982520404</v>
+        <v>-0.1732716982520407</v>
       </c>
       <c r="E63" s="6" t="n">
         <v>4.016827427516118</v>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>0.188730266225685</v>
+        <v>0.1887302662256848</v>
       </c>
       <c r="D64" s="10" t="n">
-        <v>0.3874925030886885</v>
+        <v>0.3874925030886882</v>
       </c>
       <c r="E64" s="10" t="n">
         <v>3.541964535942399</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="C65" s="6" t="n">
-        <v>0.2014242638803962</v>
+        <v>0.201424263880396</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>0.4318007876484474</v>
+        <v>0.4318007876484471</v>
       </c>
       <c r="E65" s="6" t="n">
         <v>3.487693193750408</v>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>-0.008089566292060308</v>
+        <v>-0.008089566292060549</v>
       </c>
       <c r="D66" s="10" t="n">
-        <v>-0.299505350811479</v>
+        <v>-0.2995053508114793</v>
       </c>
       <c r="E66" s="10" t="n">
         <v>4.070295846632573</v>
@@ -2544,7 +2544,7 @@
         <v>0.1435444562564117</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>0.2297718400918193</v>
+        <v>0.2297718400918196</v>
       </c>
       <c r="E67" s="6" t="n">
         <v>3.579955022499976</v>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="C68" s="10" t="n">
-        <v>0.3710389803748403</v>
+        <v>0.3710389803748401</v>
       </c>
       <c r="D68" s="10" t="n">
         <v>1.023839428932539</v>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="C69" s="6" t="n">
-        <v>0.4379368416423516</v>
+        <v>0.4379368416423511</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>1.257345811563709</v>
+        <v>1.257345811563708</v>
       </c>
       <c r="E69" s="6" t="n">
         <v>2.668787578175456</v>
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>0.2561295600870602</v>
+        <v>0.2561295600870604</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0.6227491316755296</v>
+        <v>0.6227491316755307</v>
       </c>
       <c r="E70" s="10" t="n">
         <v>3.19403194152373</v>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="C71" s="6" t="n">
-        <v>0.06870327963030926</v>
+        <v>0.06870327963030913</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>-0.03146061330364896</v>
+        <v>-0.03146061330364886</v>
       </c>
       <c r="E71" s="6" t="n">
         <v>3.709899286637851</v>
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>-0.1702129901558122</v>
+        <v>-0.1702129901558124</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>-0.8653957025945129</v>
+        <v>-0.8653957025945131</v>
       </c>
       <c r="E72" s="10" t="n">
         <v>4.400817754140449</v>
@@ -2673,7 +2673,7 @@
         </is>
       </c>
       <c r="C73" s="6" t="n">
-        <v>0.3297512055575895</v>
+        <v>0.3297512055575894</v>
       </c>
       <c r="D73" s="6" t="n">
         <v>0.8797248225490217</v>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>0.1968545892106611</v>
+        <v>0.1968545892106607</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0.4158503793437002</v>
+        <v>0.4158503793436993</v>
       </c>
       <c r="E74" s="10" t="n">
         <v>3.312643023710642</v>
@@ -2717,10 +2717,10 @@
         </is>
       </c>
       <c r="C75" s="6" t="n">
-        <v>0.06758980778364916</v>
+        <v>0.06758980778364881</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>-0.03534717676246489</v>
+        <v>-0.03534717676246557</v>
       </c>
       <c r="E75" s="6" t="n">
         <v>3.683999078482657</v>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>0.6540044283107729</v>
+        <v>0.6540044283107723</v>
       </c>
       <c r="D76" s="10" t="n">
-        <v>2.011527778084845</v>
+        <v>2.011527778084843</v>
       </c>
       <c r="E76" s="10" t="n">
         <v>1.975587422864642</v>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="C77" s="6" t="n">
-        <v>0.006452952454448452</v>
+        <v>0.006452952454448909</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>-0.2487448200186601</v>
+        <v>-0.2487448200186579</v>
       </c>
       <c r="E77" s="6" t="n">
         <v>3.812346201759584</v>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>-0.2215291203281837</v>
+        <v>-0.221529120328184</v>
       </c>
       <c r="D78" s="10" t="n">
         <v>-1.044514193083536</v>
@@ -2805,10 +2805,10 @@
         </is>
       </c>
       <c r="C79" s="6" t="n">
-        <v>0.1411200921469887</v>
+        <v>0.1411200921469886</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>0.2213096189886892</v>
+        <v>0.2213096189886891</v>
       </c>
       <c r="E79" s="6" t="n">
         <v>3.400905507101906</v>
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="C80" s="10" t="n">
-        <v>0.3952998761257199</v>
+        <v>0.3952998761257197</v>
       </c>
       <c r="D80" s="10" t="n">
         <v>1.108521867187572</v>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="C81" s="6" t="n">
-        <v>0.2943879729171557</v>
+        <v>0.2943879729171555</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>0.756289777309056</v>
+        <v>0.7562897773090556</v>
       </c>
       <c r="E81" s="6" t="n">
         <v>2.924953495632939</v>
@@ -2874,7 +2874,7 @@
         <v>0.08181834031830822</v>
       </c>
       <c r="D82" s="10" t="n">
-        <v>0.01431738798396718</v>
+        <v>0.01431738798396772</v>
       </c>
       <c r="E82" s="10" t="n">
         <v>3.530359032882403</v>
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="C83" s="6" t="n">
-        <v>0.03814190548064713</v>
+        <v>0.0381419054806469</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>-0.1381348147013408</v>
+        <v>-0.138134814701341</v>
       </c>
       <c r="E83" s="6" t="n">
         <v>3.650479895618578</v>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>0.1438407757199403</v>
+        <v>0.1438407757199399</v>
       </c>
       <c r="D84" s="10" t="n">
-        <v>0.2308061405122031</v>
+        <v>0.2308061405122022</v>
       </c>
       <c r="E84" s="10" t="n">
         <v>3.32499519208734</v>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="C85" s="6" t="n">
-        <v>-0.2015224342732495</v>
+        <v>-0.2015224342732498</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>-0.9746810354816209</v>
+        <v>-0.9746810354816215</v>
       </c>
       <c r="E85" s="6" t="n">
         <v>4.311515077894073</v>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="C86" s="10" t="n">
-        <v>0.08031292737406374</v>
+        <v>0.08031292737406381</v>
       </c>
       <c r="D86" s="10" t="n">
-        <v>0.009062757651750844</v>
+        <v>0.009062757651751619</v>
       </c>
       <c r="E86" s="10" t="n">
         <v>3.477805231722718</v>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="C87" s="6" t="n">
-        <v>0.2761003943065791</v>
+        <v>0.276100394306579</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>0.6924571487686166</v>
+        <v>0.6924571487686165</v>
       </c>
       <c r="E87" s="6" t="n">
         <v>2.897268982136119</v>
@@ -3003,10 +3003,10 @@
         </is>
       </c>
       <c r="C88" s="10" t="n">
-        <v>0.4676891542696184</v>
+        <v>0.467689154269619</v>
       </c>
       <c r="D88" s="10" t="n">
-        <v>1.361195990999545</v>
+        <v>1.361195990999548</v>
       </c>
       <c r="E88" s="10" t="n">
         <v>2.334000755373734</v>
@@ -3025,10 +3025,10 @@
         </is>
       </c>
       <c r="C89" s="6" t="n">
-        <v>-0.008740316677724069</v>
+        <v>-0.00874031667772426</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>-0.3017767891754731</v>
+        <v>-0.3017767891754732</v>
       </c>
       <c r="E89" s="6" t="n">
         <v>3.692501615622398</v>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="C90" s="10" t="n">
-        <v>0.3729168938423916</v>
+        <v>0.3729168938423915</v>
       </c>
       <c r="D90" s="10" t="n">
-        <v>1.030394268988617</v>
+        <v>1.030394268988618</v>
       </c>
       <c r="E90" s="10" t="n">
         <v>2.551512586733687</v>
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="C91" s="6" t="n">
-        <v>-0.1709996648968111</v>
+        <v>-0.1709996648968112</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>-0.8681415836973992</v>
+        <v>-0.8681415836973991</v>
       </c>
       <c r="E91" s="6" t="n">
         <v>4.117752942336272</v>
@@ -3094,7 +3094,7 @@
         <v>0.04550817125577699</v>
       </c>
       <c r="D92" s="10" t="n">
-        <v>-0.1124229303143027</v>
+        <v>-0.1124229303143021</v>
       </c>
       <c r="E92" s="10" t="n">
         <v>3.467494146153139</v>
@@ -3113,10 +3113,10 @@
         </is>
       </c>
       <c r="C93" s="6" t="n">
-        <v>0.1304211989651327</v>
+        <v>0.1304211989651325</v>
       </c>
       <c r="D93" s="6" t="n">
-        <v>0.1839652286342285</v>
+        <v>0.1839652286342284</v>
       </c>
       <c r="E93" s="6" t="n">
         <v>3.215720065550355</v>
@@ -10087,10 +10087,10 @@
         </is>
       </c>
       <c r="C410" s="10" t="n">
-        <v>0.07788233883092807</v>
+        <v>0.07788233883092817</v>
       </c>
       <c r="D410" s="10" t="n">
-        <v>0.0005788102187705261</v>
+        <v>0.000578810218771398</v>
       </c>
       <c r="E410" s="10" t="n">
         <v>3.32335848020884</v>
@@ -10109,7 +10109,7 @@
         </is>
       </c>
       <c r="C411" s="6" t="n">
-        <v>0.3910581012848007</v>
+        <v>0.3910581012848005</v>
       </c>
       <c r="D411" s="6" t="n">
         <v>1.093715990284001</v>
@@ -10131,10 +10131,10 @@
         </is>
       </c>
       <c r="C412" s="10" t="n">
-        <v>0.2615099855265646</v>
+        <v>0.2615099855265645</v>
       </c>
       <c r="D412" s="10" t="n">
-        <v>0.6415294582448865</v>
+        <v>0.6415294582448866</v>
       </c>
       <c r="E412" s="10" t="n">
         <v>2.768571285999556</v>
@@ -10156,7 +10156,7 @@
         <v>0.1161292192504072</v>
       </c>
       <c r="D413" s="6" t="n">
-        <v>0.1340792020768393</v>
+        <v>0.13407920207684</v>
       </c>
       <c r="E413" s="6" t="n">
         <v>3.174328080332662</v>
@@ -10175,10 +10175,10 @@
         </is>
       </c>
       <c r="C414" s="10" t="n">
-        <v>0.1562837832747865</v>
+        <v>0.156283783274786</v>
       </c>
       <c r="D414" s="10" t="n">
-        <v>0.2742383463874528</v>
+        <v>0.2742383463874516</v>
       </c>
       <c r="E414" s="10" t="n">
         <v>3.052209274220191</v>
@@ -10197,10 +10197,10 @@
         </is>
       </c>
       <c r="C415" s="6" t="n">
-        <v>0.1803849081050948</v>
+        <v>0.1803849081050943</v>
       </c>
       <c r="D415" s="6" t="n">
-        <v>0.3583631056822715</v>
+        <v>0.3583631056822704</v>
       </c>
       <c r="E415" s="6" t="n">
         <v>2.949646982061906</v>
@@ -10219,10 +10219,10 @@
         </is>
       </c>
       <c r="C416" s="10" t="n">
-        <v>-0.1032914642485631</v>
+        <v>-0.1032914642485634</v>
       </c>
       <c r="D416" s="10" t="n">
-        <v>-0.6318067187513351</v>
+        <v>-0.6318067187513355</v>
       </c>
       <c r="E416" s="10" t="n">
         <v>3.771261262236965</v>
@@ -10241,10 +10241,10 @@
         </is>
       </c>
       <c r="C417" s="6" t="n">
-        <v>0.2381399983390106</v>
+        <v>0.2381399983390104</v>
       </c>
       <c r="D417" s="6" t="n">
-        <v>0.5599567283114004</v>
+        <v>0.5599567283114001</v>
       </c>
       <c r="E417" s="6" t="n">
         <v>2.746890247854419</v>
@@ -10263,10 +10263,10 @@
         </is>
       </c>
       <c r="C418" s="10" t="n">
-        <v>-0.0335137714995045</v>
+        <v>-0.03351377149950473</v>
       </c>
       <c r="D418" s="10" t="n">
-        <v>-0.3882483102541299</v>
+        <v>-0.3882483102541302</v>
       </c>
       <c r="E418" s="10" t="n">
         <v>3.533831287953298</v>
@@ -10285,10 +10285,10 @@
         </is>
       </c>
       <c r="C419" s="6" t="n">
-        <v>0.1928978893237862</v>
+        <v>0.192897889323786</v>
       </c>
       <c r="D419" s="6" t="n">
-        <v>0.4020395540013659</v>
+        <v>0.4020395540013657</v>
       </c>
       <c r="E419" s="6" t="n">
         <v>2.87143160877186</v>
@@ -10307,10 +10307,10 @@
         </is>
       </c>
       <c r="C420" s="10" t="n">
-        <v>-0.05099480095425049</v>
+        <v>-0.05099480095425039</v>
       </c>
       <c r="D420" s="10" t="n">
-        <v>-0.4492656862255953</v>
+        <v>-0.4492656862255943</v>
       </c>
       <c r="E420" s="10" t="n">
         <v>3.578737836795722</v>
@@ -10329,10 +10329,10 @@
         </is>
       </c>
       <c r="C421" s="6" t="n">
-        <v>-0.05051768751358431</v>
+        <v>-0.05051768751358422</v>
       </c>
       <c r="D421" s="6" t="n">
-        <v>-0.4476003260552728</v>
+        <v>-0.4476003260552719</v>
       </c>
       <c r="E421" s="6" t="n">
         <v>3.572537771006144</v>
@@ -10351,10 +10351,10 @@
         </is>
       </c>
       <c r="C422" s="10" t="n">
-        <v>-0.01895970301240802</v>
+        <v>-0.01895970301240835</v>
       </c>
       <c r="D422" s="10" t="n">
-        <v>-0.3374474651957445</v>
+        <v>-0.3374474651957451</v>
       </c>
       <c r="E422" s="10" t="n">
         <v>3.480154588979064</v>
@@ -10373,7 +10373,7 @@
         </is>
       </c>
       <c r="C423" s="6" t="n">
-        <v>0.4460918400112888</v>
+        <v>0.4460918400112887</v>
       </c>
       <c r="D423" s="6" t="n">
         <v>1.285810759970339</v>
@@ -10395,10 +10395,10 @@
         </is>
       </c>
       <c r="C424" s="10" t="n">
-        <v>0.08225949188294053</v>
+        <v>0.08225949188294034</v>
       </c>
       <c r="D424" s="10" t="n">
-        <v>0.01585722354967307</v>
+        <v>0.01585722354967293</v>
       </c>
       <c r="E424" s="10" t="n">
         <v>3.172510393207656</v>
@@ -10417,10 +10417,10 @@
         </is>
       </c>
       <c r="C425" s="6" t="n">
-        <v>0.1526293596065119</v>
+        <v>0.1526293596065124</v>
       </c>
       <c r="D425" s="6" t="n">
-        <v>0.2614826134654658</v>
+        <v>0.2614826134654679</v>
       </c>
       <c r="E425" s="6" t="n">
         <v>2.96654574647073</v>
@@ -10439,10 +10439,10 @@
         </is>
       </c>
       <c r="C426" s="10" t="n">
-        <v>0.2215169494989993</v>
+        <v>0.2215169494989992</v>
       </c>
       <c r="D426" s="10" t="n">
-        <v>0.5019341259532979</v>
+        <v>0.5019341259532983</v>
       </c>
       <c r="E426" s="10" t="n">
         <v>2.759025393907883</v>
@@ -10464,7 +10464,7 @@
         <v>0.2937845938983916</v>
       </c>
       <c r="D427" s="6" t="n">
-        <v>0.7541836882748528</v>
+        <v>0.7541836882748532</v>
       </c>
       <c r="E427" s="6" t="n">
         <v>2.539741129321619</v>
@@ -10483,10 +10483,10 @@
         </is>
       </c>
       <c r="C428" s="10" t="n">
-        <v>0.02183580146945894</v>
+        <v>0.02183580146945871</v>
       </c>
       <c r="D428" s="10" t="n">
-        <v>-0.19505112398714</v>
+        <v>-0.1950511239871403</v>
       </c>
       <c r="E428" s="10" t="n">
         <v>3.30252141657871</v>
@@ -10505,10 +10505,10 @@
         </is>
       </c>
       <c r="C429" s="6" t="n">
-        <v>0.05675423398541721</v>
+        <v>0.05675423398541701</v>
       </c>
       <c r="D429" s="6" t="n">
-        <v>-0.07316864957817355</v>
+        <v>-0.07316864957817373</v>
       </c>
       <c r="E429" s="6" t="n">
         <v>3.188750765992238</v>
@@ -10530,7 +10530,7 @@
         <v>0.2311349635045368</v>
       </c>
       <c r="D430" s="10" t="n">
-        <v>0.5355057172714153</v>
+        <v>0.5355057172714156</v>
       </c>
       <c r="E430" s="10" t="n">
         <v>2.66753905440993</v>
@@ -10549,10 +10549,10 @@
         </is>
       </c>
       <c r="C431" s="6" t="n">
-        <v>0.2106731577274143</v>
+        <v>0.2106731577274139</v>
       </c>
       <c r="D431" s="6" t="n">
-        <v>0.4640839683755675</v>
+        <v>0.4640839683755667</v>
       </c>
       <c r="E431" s="6" t="n">
         <v>2.700399262908676</v>
@@ -10571,10 +10571,10 @@
         </is>
       </c>
       <c r="C432" s="10" t="n">
-        <v>0.3326239407133221</v>
+        <v>0.3326239407133217</v>
       </c>
       <c r="D432" s="10" t="n">
-        <v>0.8897520787536721</v>
+        <v>0.8897520787536712</v>
       </c>
       <c r="E432" s="10" t="n">
         <v>2.342349877039657</v>
@@ -10593,10 +10593,10 @@
         </is>
       </c>
       <c r="C433" s="6" t="n">
-        <v>0.07347635577377433</v>
+        <v>0.07347635577377369</v>
       </c>
       <c r="D433" s="6" t="n">
-        <v>-0.01480023398558938</v>
+        <v>-0.01480023398559108</v>
       </c>
       <c r="E433" s="6" t="n">
         <v>3.080882492887538</v>
@@ -10615,10 +10615,10 @@
         </is>
       </c>
       <c r="C434" s="10" t="n">
-        <v>0.3613194317119675</v>
+        <v>0.3613194317119672</v>
       </c>
       <c r="D434" s="10" t="n">
-        <v>0.989913431806869</v>
+        <v>0.9899134318068685</v>
       </c>
       <c r="E434" s="10" t="n">
         <v>2.22058354001811</v>
@@ -10637,10 +10637,10 @@
         </is>
       </c>
       <c r="C435" s="6" t="n">
-        <v>0.0518367046477787</v>
+        <v>0.05183670464777868</v>
       </c>
       <c r="D435" s="6" t="n">
-        <v>-0.09033324147032534</v>
+        <v>-0.09033324147032491</v>
       </c>
       <c r="E435" s="6" t="n">
         <v>3.117478008955802</v>
@@ -10659,10 +10659,10 @@
         </is>
       </c>
       <c r="C436" s="10" t="n">
-        <v>-0.006006002781806388</v>
+        <v>-0.006006002781806355</v>
       </c>
       <c r="D436" s="10" t="n">
-        <v>-0.2922326911323276</v>
+        <v>-0.2922326911323269</v>
       </c>
       <c r="E436" s="10" t="n">
         <v>3.276720357328467</v>
@@ -10681,10 +10681,10 @@
         </is>
       </c>
       <c r="C437" s="6" t="n">
-        <v>-0.07545331155628357</v>
+        <v>-0.07545331155628376</v>
       </c>
       <c r="D437" s="6" t="n">
-        <v>-0.5346378973399212</v>
+        <v>-0.5346378973399213</v>
       </c>
       <c r="E437" s="6" t="n">
         <v>3.472243353211093</v>
@@ -10703,10 +10703,10 @@
         </is>
       </c>
       <c r="C438" s="10" t="n">
-        <v>0.3461096809770542</v>
+        <v>0.3461096809770537</v>
       </c>
       <c r="D438" s="10" t="n">
-        <v>0.9368239337640342</v>
+        <v>0.9368239337640331</v>
       </c>
       <c r="E438" s="10" t="n">
         <v>2.247057985194922</v>
@@ -10725,10 +10725,10 @@
         </is>
       </c>
       <c r="C439" s="6" t="n">
-        <v>0.1376949571143432</v>
+        <v>0.1376949571143428</v>
       </c>
       <c r="D439" s="6" t="n">
-        <v>0.2093542159856225</v>
+        <v>0.2093542159856217</v>
       </c>
       <c r="E439" s="6" t="n">
         <v>2.845925000339224</v>
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="C440" s="10" t="n">
-        <v>-0.2578842793540234</v>
+        <v>-0.2578842793540237</v>
       </c>
       <c r="D440" s="10" t="n">
         <v>-1.171411548443796</v>
@@ -10769,10 +10769,10 @@
         </is>
       </c>
       <c r="C441" s="6" t="n">
-        <v>-0.1553472687292359</v>
+        <v>-0.155347268729236</v>
       </c>
       <c r="D441" s="6" t="n">
-        <v>-0.8135070357559467</v>
+        <v>-0.8135070357559469</v>
       </c>
       <c r="E441" s="6" t="n">
         <v>3.667538478663727</v>
@@ -10794,7 +10794,7 @@
         <v>0.1374707240015131</v>
       </c>
       <c r="D442" s="10" t="n">
-        <v>0.2085715323235287</v>
+        <v>0.2085715323235294</v>
       </c>
       <c r="E442" s="10" t="n">
         <v>2.815964128078679</v>
@@ -10813,10 +10813,10 @@
         </is>
       </c>
       <c r="C443" s="6" t="n">
-        <v>-0.212537583559027</v>
+        <v>-0.2125375835590273</v>
       </c>
       <c r="D443" s="6" t="n">
-        <v>-1.013129314920314</v>
+        <v>-1.013129314920315</v>
       </c>
       <c r="E443" s="6" t="n">
         <v>3.829928551872102</v>
@@ -10835,7 +10835,7 @@
         </is>
       </c>
       <c r="C444" s="10" t="n">
-        <v>0.3701567929919641</v>
+        <v>0.3701567929919639</v>
       </c>
       <c r="D444" s="10" t="n">
         <v>1.020760161812854</v>
@@ -10857,10 +10857,10 @@
         </is>
       </c>
       <c r="C445" s="6" t="n">
-        <v>0.1975084322922332</v>
+        <v>0.1975084322922331</v>
       </c>
       <c r="D445" s="6" t="n">
-        <v>0.4181326127349263</v>
+        <v>0.4181326127349264</v>
       </c>
       <c r="E445" s="6" t="n">
         <v>2.602524724491352</v>
@@ -10879,10 +10879,10 @@
         </is>
       </c>
       <c r="C446" s="10" t="n">
-        <v>0.06526387162342225</v>
+        <v>0.065263871623422</v>
       </c>
       <c r="D446" s="10" t="n">
-        <v>-0.04346583599483985</v>
+        <v>-0.04346583599484019</v>
       </c>
       <c r="E446" s="10" t="n">
         <v>2.975486986075317</v>
@@ -10901,10 +10901,10 @@
         </is>
       </c>
       <c r="C447" s="6" t="n">
-        <v>-0.0462034959028541</v>
+        <v>-0.04620349590285416</v>
       </c>
       <c r="D447" s="6" t="n">
-        <v>-0.4325416790684731</v>
+        <v>-0.4325416790684728</v>
       </c>
       <c r="E447" s="6" t="n">
         <v>3.289943450717048</v>
@@ -10923,10 +10923,10 @@
         </is>
       </c>
       <c r="C448" s="10" t="n">
-        <v>-0.1050071297793933</v>
+        <v>-0.1050071297793935</v>
       </c>
       <c r="D448" s="10" t="n">
-        <v>-0.6377952338446226</v>
+        <v>-0.6377952338446229</v>
       </c>
       <c r="E448" s="10" t="n">
         <v>3.46051362089841</v>
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="C449" s="6" t="n">
-        <v>-0.2600148323684252</v>
+        <v>-0.2600148323684253</v>
       </c>
       <c r="D449" s="6" t="n">
         <v>-1.17884822456424</v>
@@ -10967,10 +10967,10 @@
         </is>
       </c>
       <c r="C450" s="10" t="n">
-        <v>-0.01449349511822251</v>
+        <v>-0.01449349511822333</v>
       </c>
       <c r="D450" s="10" t="n">
-        <v>-0.3218582067397869</v>
+        <v>-0.3218582067397892</v>
       </c>
       <c r="E450" s="10" t="n">
         <v>3.187999605685978</v>
@@ -10989,10 +10989,10 @@
         </is>
       </c>
       <c r="C451" s="6" t="n">
-        <v>0.296158477872677</v>
+        <v>0.2961584778726761</v>
       </c>
       <c r="D451" s="6" t="n">
-        <v>0.7624697089206383</v>
+        <v>0.7624697089206355</v>
       </c>
       <c r="E451" s="6" t="n">
         <v>2.246862043008139</v>
@@ -11011,10 +11011,10 @@
         </is>
       </c>
       <c r="C452" s="10" t="n">
-        <v>0.1053227918176789</v>
+        <v>0.1053227918176786</v>
       </c>
       <c r="D452" s="10" t="n">
-        <v>0.09635946438758543</v>
+        <v>0.09635946438758514</v>
       </c>
       <c r="E452" s="10" t="n">
         <v>2.764306958431566</v>
@@ -11033,10 +11033,10 @@
         </is>
       </c>
       <c r="C453" s="6" t="n">
-        <v>0.07946491681923999</v>
+        <v>0.07946491681923955</v>
       </c>
       <c r="D453" s="6" t="n">
-        <v>0.006102784442770074</v>
+        <v>0.006102784442769058</v>
       </c>
       <c r="E453" s="6" t="n">
         <v>2.834324436371338</v>
@@ -11055,10 +11055,10 @@
         </is>
       </c>
       <c r="C454" s="10" t="n">
-        <v>-0.1595218571553502</v>
+        <v>-0.1595218571553506</v>
       </c>
       <c r="D454" s="10" t="n">
-        <v>-0.8280783990833616</v>
+        <v>-0.8280783990833627</v>
       </c>
       <c r="E454" s="10" t="n">
         <v>3.515158920699321</v>
@@ -11077,10 +11077,10 @@
         </is>
       </c>
       <c r="C455" s="6" t="n">
-        <v>-0.03355234036725438</v>
+        <v>-0.03355234036725408</v>
       </c>
       <c r="D455" s="6" t="n">
-        <v>-0.3883829345398666</v>
+        <v>-0.388382934539865</v>
       </c>
       <c r="E455" s="6" t="n">
         <v>3.148166523063308</v>
@@ -11099,10 +11099,10 @@
         </is>
       </c>
       <c r="C456" s="10" t="n">
-        <v>0.09175167613555352</v>
+        <v>0.09175167613555332</v>
       </c>
       <c r="D456" s="10" t="n">
-        <v>0.04898960724775462</v>
+        <v>0.04898960724775448</v>
       </c>
       <c r="E456" s="10" t="n">
         <v>2.77757740079275</v>
@@ -11124,7 +11124,7 @@
         <v>-0.2653171919452743</v>
       </c>
       <c r="D457" s="6" t="n">
-        <v>-1.197356062942641</v>
+        <v>-1.19735606294264</v>
       </c>
       <c r="E457" s="6" t="n">
         <v>3.797866481823048</v>
@@ -11143,10 +11143,10 @@
         </is>
       </c>
       <c r="C458" s="10" t="n">
-        <v>0.2903696683450568</v>
+        <v>0.2903696683450571</v>
       </c>
       <c r="D458" s="10" t="n">
-        <v>0.7422639213674282</v>
+        <v>0.7422639213674297</v>
       </c>
       <c r="E458" s="10" t="n">
         <v>2.179956210406286</v>
@@ -11165,10 +11165,10 @@
         </is>
       </c>
       <c r="C459" s="6" t="n">
-        <v>0.1628527778734648</v>
+        <v>0.1628527778734649</v>
       </c>
       <c r="D459" s="6" t="n">
-        <v>0.297167362909032</v>
+        <v>0.2971673629090327</v>
       </c>
       <c r="E459" s="6" t="n">
         <v>2.544473652995541</v>
@@ -11187,10 +11187,10 @@
         </is>
       </c>
       <c r="C460" s="10" t="n">
-        <v>0.02581104145732232</v>
+        <v>0.02581104145732221</v>
       </c>
       <c r="D460" s="10" t="n">
-        <v>-0.1811755845891779</v>
+        <v>-0.1811755845891778</v>
       </c>
       <c r="E460" s="10" t="n">
         <v>2.941840132704634</v>
@@ -11209,10 +11209,10 @@
         </is>
       </c>
       <c r="C461" s="6" t="n">
-        <v>-0.1479351744163979</v>
+        <v>-0.147935174416398</v>
       </c>
       <c r="D461" s="6" t="n">
-        <v>-0.7876351872705244</v>
+        <v>-0.7876351872705242</v>
       </c>
       <c r="E461" s="6" t="n">
         <v>3.442700954195591</v>
@@ -11231,10 +11231,10 @@
         </is>
       </c>
       <c r="C462" s="10" t="n">
-        <v>-0.194570725763494</v>
+        <v>-0.1945707257634942</v>
       </c>
       <c r="D462" s="10" t="n">
-        <v>-0.9504161594980943</v>
+        <v>-0.9504161594980945</v>
       </c>
       <c r="E462" s="10" t="n">
         <v>3.561988280371084</v>
@@ -11253,10 +11253,10 @@
         </is>
       </c>
       <c r="C463" s="6" t="n">
-        <v>0.03754411380386542</v>
+        <v>0.0375441138038651</v>
       </c>
       <c r="D463" s="6" t="n">
-        <v>-0.140221401168644</v>
+        <v>-0.1402214011686446</v>
       </c>
       <c r="E463" s="6" t="n">
         <v>2.875239265631446</v>
@@ -11275,10 +11275,10 @@
         </is>
       </c>
       <c r="C464" s="10" t="n">
-        <v>-0.05698587470548247</v>
+        <v>-0.05698587470548244</v>
       </c>
       <c r="D464" s="10" t="n">
-        <v>-0.4701774752308161</v>
+        <v>-0.4701774752308154</v>
       </c>
       <c r="E464" s="10" t="n">
         <v>3.142236736147904</v>
@@ -11297,10 +11297,10 @@
         </is>
       </c>
       <c r="C465" s="6" t="n">
-        <v>-0.2595909595057668</v>
+        <v>-0.2595909595057666</v>
       </c>
       <c r="D465" s="6" t="n">
-        <v>-1.177368700152255</v>
+        <v>-1.177368700152254</v>
       </c>
       <c r="E465" s="6" t="n">
         <v>3.711545071373304</v>
@@ -11319,10 +11319,10 @@
         </is>
       </c>
       <c r="C466" s="10" t="n">
-        <v>0.03705760847767477</v>
+        <v>0.03705760847767489</v>
       </c>
       <c r="D466" s="10" t="n">
-        <v>-0.1419195436308567</v>
+        <v>-0.1419195436308557</v>
       </c>
       <c r="E466" s="10" t="n">
         <v>2.84876425828431</v>
@@ -11341,10 +11341,10 @@
         </is>
       </c>
       <c r="C467" s="6" t="n">
-        <v>0.07716485381282258</v>
+        <v>0.0771648538128224</v>
       </c>
       <c r="D467" s="6" t="n">
-        <v>-0.001925564779107574</v>
+        <v>-0.001925564779107671</v>
       </c>
       <c r="E467" s="6" t="n">
         <v>2.710966397390389</v>
@@ -11363,10 +11363,10 @@
         </is>
       </c>
       <c r="C468" s="10" t="n">
-        <v>-0.07520023319638849</v>
+        <v>-0.07520023319638872</v>
       </c>
       <c r="D468" s="10" t="n">
-        <v>-0.5337545296025727</v>
+        <v>-0.533754529602573</v>
       </c>
       <c r="E468" s="10" t="n">
         <v>3.140913168461501</v>
@@ -11385,10 +11385,10 @@
         </is>
       </c>
       <c r="C469" s="6" t="n">
-        <v>-0.1548019896071578</v>
+        <v>-0.154801989607158</v>
       </c>
       <c r="D469" s="6" t="n">
-        <v>-0.8116037438881903</v>
+        <v>-0.8116037438881907</v>
       </c>
       <c r="E469" s="6" t="n">
         <v>3.362777749487051</v>
@@ -11407,10 +11407,10 @@
         </is>
       </c>
       <c r="C470" s="10" t="n">
-        <v>-0.08541478028250629</v>
+        <v>-0.08541478028250665</v>
       </c>
       <c r="D470" s="10" t="n">
-        <v>-0.5694083142692803</v>
+        <v>-0.569408314269281</v>
       </c>
       <c r="E470" s="10" t="n">
         <v>3.150839156484102</v>
@@ -11429,10 +11429,10 @@
         </is>
       </c>
       <c r="C471" s="6" t="n">
-        <v>-0.008032968735419369</v>
+        <v>-0.008032968735419728</v>
       </c>
       <c r="D471" s="6" t="n">
-        <v>-0.2993077975494376</v>
+        <v>-0.2993077975494383</v>
       </c>
       <c r="E471" s="6" t="n">
         <v>2.92059648904186</v>
@@ -11451,10 +11451,10 @@
         </is>
       </c>
       <c r="C472" s="10" t="n">
-        <v>-0.07505570718531482</v>
+        <v>-0.07505570718531504</v>
       </c>
       <c r="D472" s="10" t="n">
-        <v>-0.5332500628617456</v>
+        <v>-0.5332500628617458</v>
       </c>
       <c r="E472" s="10" t="n">
         <v>3.073976804822982</v>
@@ -11473,10 +11473,10 @@
         </is>
       </c>
       <c r="C473" s="6" t="n">
-        <v>-0.1110204877755914</v>
+        <v>-0.1110204877755915</v>
       </c>
       <c r="D473" s="6" t="n">
-        <v>-0.6587848058063253</v>
+        <v>-0.6587848058063251</v>
       </c>
       <c r="E473" s="6" t="n">
         <v>3.144739898115974</v>
@@ -11495,10 +11495,10 @@
         </is>
       </c>
       <c r="C474" s="10" t="n">
-        <v>-0.0499281755806172</v>
+        <v>-0.0499281755806174</v>
       </c>
       <c r="D474" s="10" t="n">
-        <v>-0.4455426399592314</v>
+        <v>-0.4455426399592317</v>
       </c>
       <c r="E474" s="10" t="n">
         <v>2.902547253539049</v>
@@ -11517,10 +11517,10 @@
         </is>
       </c>
       <c r="C475" s="6" t="n">
-        <v>-0.1293234646261053</v>
+        <v>-0.1293234646261056</v>
       </c>
       <c r="D475" s="6" t="n">
-        <v>-0.7226711817646719</v>
+        <v>-0.7226711817646724</v>
       </c>
       <c r="E475" s="6" t="n">
         <v>3.126615640748661</v>
@@ -11539,10 +11539,10 @@
         </is>
       </c>
       <c r="C476" s="10" t="n">
-        <v>0.07524108809168267</v>
+        <v>0.07524108809168237</v>
       </c>
       <c r="D476" s="10" t="n">
-        <v>-0.008640451713637738</v>
+        <v>-0.00864045171363827</v>
       </c>
       <c r="E476" s="10" t="n">
         <v>2.47370836603897</v>
@@ -11561,10 +11561,10 @@
         </is>
       </c>
       <c r="C477" s="6" t="n">
-        <v>0.2164548713290022</v>
+        <v>0.2164548713290017</v>
       </c>
       <c r="D477" s="6" t="n">
-        <v>0.4842649876628295</v>
+        <v>0.4842649876628282</v>
       </c>
       <c r="E477" s="6" t="n">
         <v>2.062821565839493</v>
@@ -11583,10 +11583,10 @@
         </is>
       </c>
       <c r="C478" s="10" t="n">
-        <v>0.03842017539961994</v>
+        <v>0.03842017539961958</v>
       </c>
       <c r="D478" s="10" t="n">
-        <v>-0.1371635160537715</v>
+        <v>-0.1371635160537722</v>
       </c>
       <c r="E478" s="10" t="n">
         <v>2.570579132305955</v>
@@ -11605,10 +11605,10 @@
         </is>
       </c>
       <c r="C479" s="6" t="n">
-        <v>-0.1862811502561021</v>
+        <v>-0.1862811502561024</v>
       </c>
       <c r="D479" s="6" t="n">
-        <v>-0.9214814708009675</v>
+        <v>-0.921481470800968</v>
       </c>
       <c r="E479" s="6" t="n">
         <v>3.219384056002765</v>
@@ -11627,10 +11627,10 @@
         </is>
       </c>
       <c r="C480" s="10" t="n">
-        <v>-0.01189478021439528</v>
+        <v>-0.01189478021439537</v>
       </c>
       <c r="D480" s="10" t="n">
-        <v>-0.3127874157580563</v>
+        <v>-0.3127874157580561</v>
       </c>
       <c r="E480" s="10" t="n">
         <v>2.687596615808355</v>
@@ -11649,7 +11649,7 @@
         </is>
       </c>
       <c r="C481" s="6" t="n">
-        <v>-0.2113263348086612</v>
+        <v>-0.2113263348086614</v>
       </c>
       <c r="D481" s="6" t="n">
         <v>-1.008901462059168</v>
@@ -11671,10 +11671,10 @@
         </is>
       </c>
       <c r="C482" s="10" t="n">
-        <v>0.07352598229415171</v>
+        <v>0.07352598229415128</v>
       </c>
       <c r="D482" s="10" t="n">
-        <v>-0.01462701306288223</v>
+        <v>-0.0146270130628832</v>
       </c>
       <c r="E482" s="10" t="n">
         <v>2.39644255644385</v>
@@ -11693,7 +11693,7 @@
         </is>
       </c>
       <c r="C483" s="6" t="n">
-        <v>-0.1135221192000784</v>
+        <v>-0.1135221192000786</v>
       </c>
       <c r="D483" s="6" t="n">
         <v>-0.6675167277772317</v>
@@ -11718,7 +11718,7 @@
         <v>-0.1822258140852475</v>
       </c>
       <c r="D484" s="10" t="n">
-        <v>-0.9073263563971908</v>
+        <v>-0.9073263563971905</v>
       </c>
       <c r="E484" s="10" t="n">
         <v>3.097725541293023</v>
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="C485" s="6" t="n">
-        <v>-0.07214579889848736</v>
+        <v>-0.07214579889848752</v>
       </c>
       <c r="D485" s="6" t="n">
         <v>-0.5230930541775901</v>
@@ -11759,10 +11759,10 @@
         </is>
       </c>
       <c r="C486" s="10" t="n">
-        <v>0.019491528057719</v>
+        <v>0.0194915280577184</v>
       </c>
       <c r="D486" s="10" t="n">
-        <v>-0.2032337892308743</v>
+        <v>-0.2032337892308759</v>
       </c>
       <c r="E486" s="10" t="n">
         <v>2.4251550896128</v>
@@ -11781,7 +11781,7 @@
         </is>
       </c>
       <c r="C487" s="6" t="n">
-        <v>-0.468842375993519</v>
+        <v>-0.4688423759935191</v>
       </c>
       <c r="D487" s="6" t="n">
         <v>-1.90775888600761</v>
@@ -11803,10 +11803,10 @@
         </is>
       </c>
       <c r="C488" s="10" t="n">
-        <v>0.1697690248796294</v>
+        <v>0.169769024879629</v>
       </c>
       <c r="D488" s="10" t="n">
-        <v>0.3213084608334503</v>
+        <v>0.3213084608334495</v>
       </c>
       <c r="E488" s="10" t="n">
         <v>1.958681998090855</v>
@@ -11825,10 +11825,10 @@
         </is>
       </c>
       <c r="C489" s="6" t="n">
-        <v>-0.4435858680153095</v>
+        <v>-0.4435858680153092</v>
       </c>
       <c r="D489" s="6" t="n">
-        <v>-1.819601272234222</v>
+        <v>-1.81960127223422</v>
       </c>
       <c r="E489" s="6" t="n">
         <v>3.564578022965704</v>
@@ -11847,7 +11847,7 @@
         </is>
       </c>
       <c r="C490" s="10" t="n">
-        <v>-0.313928368191851</v>
+        <v>-0.3139283681918512</v>
       </c>
       <c r="D490" s="10" t="n">
         <v>-1.367032936099974</v>
@@ -11869,10 +11869,10 @@
         </is>
       </c>
       <c r="C491" s="6" t="n">
-        <v>-0.1620442796505573</v>
+        <v>-0.1620442796505569</v>
       </c>
       <c r="D491" s="6" t="n">
-        <v>-0.8368828920994837</v>
+        <v>-0.8368828920994819</v>
       </c>
       <c r="E491" s="6" t="n">
         <v>2.652181683118239</v>
@@ -11894,7 +11894,7 @@
         <v>-0.1102158658960353</v>
       </c>
       <c r="D492" s="10" t="n">
-        <v>-0.6559762803778408</v>
+        <v>-0.6559762803778405</v>
       </c>
       <c r="E492" s="10" t="n">
         <v>2.496746355315755</v>
@@ -11913,10 +11913,10 @@
         </is>
       </c>
       <c r="C493" s="6" t="n">
-        <v>-0.1261922287452327</v>
+        <v>-0.1261922287452331</v>
       </c>
       <c r="D493" s="6" t="n">
-        <v>-0.7117416311055903</v>
+        <v>-0.7117416311055911</v>
       </c>
       <c r="E493" s="6" t="n">
         <v>2.53692953967824</v>
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="C494" s="10" t="n">
-        <v>-0.1240576588768293</v>
+        <v>-0.1240576588768294</v>
       </c>
       <c r="D494" s="10" t="n">
         <v>-0.7042909341924075</v>
@@ -11957,10 +11957,10 @@
         </is>
       </c>
       <c r="C495" s="6" t="n">
-        <v>-0.1721870121769944</v>
+        <v>-0.1721870121769946</v>
       </c>
       <c r="D495" s="6" t="n">
-        <v>-0.8722860086920023</v>
+        <v>-0.8722860086920025</v>
       </c>
       <c r="E495" s="6" t="n">
         <v>2.595423456266408</v>
@@ -11979,7 +11979,7 @@
         </is>
       </c>
       <c r="C496" s="10" t="n">
-        <v>-0.2716910695887764</v>
+        <v>-0.2716910695887765</v>
       </c>
       <c r="D496" s="10" t="n">
         <v>-1.219604025488353</v>
@@ -12001,7 +12001,7 @@
         </is>
       </c>
       <c r="C497" s="6" t="n">
-        <v>-0.3886449045506206</v>
+        <v>-0.3886449045506208</v>
       </c>
       <c r="D497" s="6" t="n">
         <v>-1.627830333764158</v>
@@ -12023,10 +12023,10 @@
         </is>
       </c>
       <c r="C498" s="10" t="n">
-        <v>-0.302235815670876</v>
+        <v>-0.3022358156708759</v>
       </c>
       <c r="D498" s="10" t="n">
-        <v>-1.326220186765881</v>
+        <v>-1.32622018676588</v>
       </c>
       <c r="E498" s="10" t="n">
         <v>2.661970745078957</v>
@@ -12045,10 +12045,10 @@
         </is>
       </c>
       <c r="C499" s="6" t="n">
-        <v>-0.1782876436469442</v>
+        <v>-0.1782876436469445</v>
       </c>
       <c r="D499" s="6" t="n">
-        <v>-0.893580207928319</v>
+        <v>-0.8935802079283194</v>
       </c>
       <c r="E499" s="6" t="n">
         <v>2.269273199170042</v>
@@ -12067,10 +12067,10 @@
         </is>
       </c>
       <c r="C500" s="10" t="n">
-        <v>-0.3614549117986997</v>
+        <v>-0.3614549117987</v>
       </c>
       <c r="D500" s="10" t="n">
-        <v>-1.532923908790716</v>
+        <v>-1.532923908790717</v>
       </c>
       <c r="E500" s="10" t="n">
         <v>2.575674189479364</v>
@@ -12089,7 +12089,7 @@
         </is>
       </c>
       <c r="C501" s="6" t="n">
-        <v>-0.4860099001753612</v>
+        <v>-0.4860099001753615</v>
       </c>
       <c r="D501" s="6" t="n">
         <v>-1.967681974645751</v>
@@ -12111,10 +12111,10 @@
         </is>
       </c>
       <c r="C502" s="10" t="n">
-        <v>-0.5876169312034601</v>
+        <v>-0.5876169312034606</v>
       </c>
       <c r="D502" s="10" t="n">
-        <v>-2.322340401921763</v>
+        <v>-2.322340401921764</v>
       </c>
       <c r="E502" s="10" t="n">
         <v>1.202690424257375</v>
